--- a/sample-data/split/Media.xlsx
+++ b/sample-data/split/Media.xlsx
@@ -459,8 +459,8 @@
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation sqref="A2:A500" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" errorTitle="Unrecognised grade" error="Pick a grade from the list. A different spelling makes the row disappear from the site." type="list">
-      <formula1>"JK,Grade 1,Grade 2,Grade 3,Grade 4,Grade 5,Grade 6,Grade 7,Grade 8,Grade 9,Grade 10,Grade 11,Grade 12"</formula1>
+    <dataValidation sqref="A2:A1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" errorTitle="Unrecognised grade" error="Pick a grade from the list. A different spelling makes the row disappear from the site." type="list">
+      <formula1>"JK,SK,Grade 1,Grade 2,Grade 3,Grade 4,Grade 5,Grade 6,Grade 7,Grade 8,Grade 9,Grade 10,Grade 11,Grade 12"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
